--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260728.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260728.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8,316,172</t>
+          <t>7,227,124</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7,227,124</t>
+          <t>8,316,172</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>25,737,970</t>
+          <t>69,792,636</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>69,792,636</t>
+          <t>25,737,970</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>1,779,256</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,779,256</t>
+          <t>648</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
